--- a/10423정승환-CFDsimulation_Result.xlsx
+++ b/10423정승환-CFDsimulation_Result.xlsx
@@ -458,818 +458,818 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15deg</t>
+          <t>-175deg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>787.321396642381</v>
+        <v>24.8656837827619</v>
       </c>
       <c r="C2" t="n">
-        <v>1315.492302624502</v>
+        <v>335.6092083623426</v>
       </c>
       <c r="D2" t="n">
-        <v>1996.752592904762</v>
+        <v>1356.584471957143</v>
       </c>
       <c r="E2" t="n">
-        <v>9950.227710343732</v>
+        <v>10093.99326714208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25deg</t>
+          <t>-170deg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1260.921941785714</v>
+        <v>224.3542925947619</v>
       </c>
       <c r="C3" t="n">
-        <v>2590.27922831642</v>
+        <v>949.5655674544259</v>
       </c>
       <c r="D3" t="n">
-        <v>2081.770262552381</v>
+        <v>1243.019115852381</v>
       </c>
       <c r="E3" t="n">
-        <v>9935.443056978445</v>
+        <v>10626.70122817451</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-20deg</t>
+          <t>-165deg</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-557.1148521685715</v>
+        <v>441.6166530698573</v>
       </c>
       <c r="C4" t="n">
-        <v>2320.321104358078</v>
+        <v>1589.894158691292</v>
       </c>
       <c r="D4" t="n">
-        <v>1449.623088628571</v>
+        <v>1630.975732561904</v>
       </c>
       <c r="E4" t="n">
-        <v>8215.50712509364</v>
+        <v>9829.555533804167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-155deg</t>
+          <t>-160deg</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>871.4113540523811</v>
+        <v>629.9694770180953</v>
       </c>
       <c r="C5" t="n">
-        <v>2781.444646165929</v>
+        <v>2205.720489459218</v>
       </c>
       <c r="D5" t="n">
-        <v>1841.234304180952</v>
+        <v>1522.351259352381</v>
       </c>
       <c r="E5" t="n">
-        <v>8916.653254498591</v>
+        <v>9668.558856017688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>135deg</t>
+          <t>-155deg</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-466.2586414638096</v>
+        <v>871.4113540523811</v>
       </c>
       <c r="C6" t="n">
-        <v>2399.16475114783</v>
+        <v>2781.444646165929</v>
       </c>
       <c r="D6" t="n">
-        <v>985.2897601190475</v>
+        <v>1841.234304180952</v>
       </c>
       <c r="E6" t="n">
-        <v>4517.062101724706</v>
+        <v>8916.653254498591</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-135deg</t>
+          <t>-150deg</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1221.423509821905</v>
+        <v>1033.459658532281</v>
       </c>
       <c r="C7" t="n">
-        <v>4147.671503725298</v>
+        <v>3281.93771655943</v>
       </c>
       <c r="D7" t="n">
-        <v>1253.288345076191</v>
+        <v>1751.622568120952</v>
       </c>
       <c r="E7" t="n">
-        <v>6328.465783449878</v>
+        <v>8423.722641613707</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-5deg</t>
+          <t>-145deg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-135.3992166495239</v>
+        <v>1153.835657014286</v>
       </c>
       <c r="C8" t="n">
-        <v>840.7750207239716</v>
+        <v>3685.894746668404</v>
       </c>
       <c r="D8" t="n">
-        <v>1530.761688961904</v>
+        <v>1592.303583604762</v>
       </c>
       <c r="E8" t="n">
-        <v>9132.357629053256</v>
+        <v>7972.101645429689</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-15deg</t>
+          <t>-140deg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-436.1635462228571</v>
+        <v>1210.006117790476</v>
       </c>
       <c r="C9" t="n">
-        <v>1822.424494995602</v>
+        <v>3995.641808978025</v>
       </c>
       <c r="D9" t="n">
-        <v>1505.520628572858</v>
+        <v>1370.433535438095</v>
       </c>
       <c r="E9" t="n">
-        <v>8475.975376894323</v>
+        <v>7344.365517704073</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-125deg</t>
+          <t>-135deg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1098.074450099048</v>
+        <v>1221.423509821905</v>
       </c>
       <c r="C10" t="n">
-        <v>4069.355993129425</v>
+        <v>4147.671503725298</v>
       </c>
       <c r="D10" t="n">
-        <v>871.1367913333336</v>
+        <v>1253.288345076191</v>
       </c>
       <c r="E10" t="n">
-        <v>4716.844970247713</v>
+        <v>6328.465783449878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-100deg</t>
+          <t>-130deg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-148.9346854295238</v>
+        <v>77.61156191095239</v>
       </c>
       <c r="C11" t="n">
-        <v>1975.652546751248</v>
+        <v>360.3248032899532</v>
       </c>
       <c r="D11" t="n">
-        <v>856.2680278571428</v>
+        <v>1357.749577789048</v>
       </c>
       <c r="E11" t="n">
-        <v>2162.755050429641</v>
+        <v>10136.7001419032</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-55deg</t>
+          <t>-125deg</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>167.4072403285714</v>
+        <v>1098.074450099048</v>
       </c>
       <c r="C12" t="n">
-        <v>3888.536470008535</v>
+        <v>4069.355993129425</v>
       </c>
       <c r="D12" t="n">
-        <v>129.2094811428573</v>
+        <v>871.1367913333336</v>
       </c>
       <c r="E12" t="n">
-        <v>3735.514906768211</v>
+        <v>4716.844970247713</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>60deg</t>
+          <t>-120deg</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2093.8828703</v>
+        <v>920.8593294404761</v>
       </c>
       <c r="C13" t="n">
-        <v>4474.832293693121</v>
+        <v>3793.715653852181</v>
       </c>
       <c r="D13" t="n">
-        <v>1265.74441652381</v>
+        <v>706.3845832857145</v>
       </c>
       <c r="E13" t="n">
-        <v>5136.605277149652</v>
+        <v>3970.00371330998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>-110deg</t>
+          <t>-115deg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>536.8224892209523</v>
+        <v>769.0109499289049</v>
       </c>
       <c r="C14" t="n">
-        <v>2779.314599025009</v>
+        <v>3324.227614428866</v>
       </c>
       <c r="D14" t="n">
-        <v>478.0070633809523</v>
+        <v>546.8015591904763</v>
       </c>
       <c r="E14" t="n">
-        <v>2609.920665764645</v>
+        <v>3259.992313578076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30deg</t>
+          <t>-110deg</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1464.965918666667</v>
+        <v>536.8224892209523</v>
       </c>
       <c r="C15" t="n">
-        <v>3157.554704016287</v>
+        <v>2779.314599025009</v>
       </c>
       <c r="D15" t="n">
-        <v>1968.68173028381</v>
+        <v>478.0070633809523</v>
       </c>
       <c r="E15" t="n">
-        <v>9642.658386653295</v>
+        <v>2609.920665764645</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>55deg</t>
+          <t>-105deg</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2100.640326898572</v>
+        <v>94.03387599523811</v>
       </c>
       <c r="C16" t="n">
-        <v>4589.585568405176</v>
+        <v>2261.819509307346</v>
       </c>
       <c r="D16" t="n">
-        <v>1464.569943661905</v>
+        <v>611.7580402857143</v>
       </c>
       <c r="E16" t="n">
-        <v>5881.208929283049</v>
+        <v>2007.44154839647</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>165deg</t>
+          <t>-100deg</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-585.1545893257141</v>
+        <v>-148.9346854295238</v>
       </c>
       <c r="C17" t="n">
-        <v>1724.848083635922</v>
+        <v>1975.652546751248</v>
       </c>
       <c r="D17" t="n">
-        <v>1449.866905352381</v>
+        <v>856.2680278571428</v>
       </c>
       <c r="E17" t="n">
-        <v>8537.893541451966</v>
+        <v>2162.755050429641</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100deg</t>
+          <t>-95deg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>791.0753256652381</v>
+        <v>-1221.609143542381</v>
       </c>
       <c r="C18" t="n">
-        <v>908.9109659641111</v>
+        <v>2325.759912078654</v>
       </c>
       <c r="D18" t="n">
-        <v>253.500609904762</v>
+        <v>1902.846852047619</v>
       </c>
       <c r="E18" t="n">
-        <v>2051.938571582224</v>
+        <v>6603.491254678953</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>160deg</t>
+          <t>-90deg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-703.4080177509524</v>
+        <v>-568.1584215114284</v>
       </c>
       <c r="C19" t="n">
-        <v>2190.129894216443</v>
+        <v>50852.67328029735</v>
       </c>
       <c r="D19" t="n">
-        <v>1644.687025219047</v>
+        <v>8923.982683171425</v>
       </c>
       <c r="E19" t="n">
-        <v>8197.082455689164</v>
+        <v>141359.256151088</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>-120deg</t>
+          <t>-85deg</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>920.8593294404761</v>
+        <v>-110821.4214485644</v>
       </c>
       <c r="C20" t="n">
-        <v>3793.715653852181</v>
+        <v>100463.1227120362</v>
       </c>
       <c r="D20" t="n">
-        <v>706.3845832857145</v>
+        <v>-10137.39880652381</v>
       </c>
       <c r="E20" t="n">
-        <v>3970.00371330998</v>
+        <v>84721.29026376741</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>105deg</t>
+          <t>-80deg</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>607.5388687066667</v>
+        <v>-17887.48295795</v>
       </c>
       <c r="C21" t="n">
-        <v>555.5002186796906</v>
+        <v>9645.975405100715</v>
       </c>
       <c r="D21" t="n">
-        <v>251.138499</v>
+        <v>162.8205356666666</v>
       </c>
       <c r="E21" t="n">
-        <v>2157.859867789057</v>
+        <v>14647.64036153058</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45deg</t>
+          <t>-75deg</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1968.132179120476</v>
+        <v>-4822.952057147143</v>
       </c>
       <c r="C22" t="n">
-        <v>4409.554495160801</v>
+        <v>4849.899016941325</v>
       </c>
       <c r="D22" t="n">
-        <v>1711.072369461905</v>
+        <v>599.2291788571426</v>
       </c>
       <c r="E22" t="n">
-        <v>7598.926211207297</v>
+        <v>4890.736974691083</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>-105deg</t>
+          <t>-70deg</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94.03387599523811</v>
+        <v>-1834.784777042381</v>
       </c>
       <c r="C23" t="n">
-        <v>2261.819509307346</v>
+        <v>4201.587417343285</v>
       </c>
       <c r="D23" t="n">
-        <v>611.7580402857143</v>
+        <v>772.542310238095</v>
       </c>
       <c r="E23" t="n">
-        <v>2007.44154839647</v>
+        <v>2060.111725459966</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>-25deg</t>
+          <t>-65deg</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-615.5435602295237</v>
+        <v>-636.9687476904762</v>
       </c>
       <c r="C24" t="n">
-        <v>2798.012092609699</v>
+        <v>3704.736970527907</v>
       </c>
       <c r="D24" t="n">
-        <v>1390.018021810476</v>
+        <v>535.8102426190477</v>
       </c>
       <c r="E24" t="n">
-        <v>7744.967730938922</v>
+        <v>2263.404382377319</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-80deg</t>
+          <t>-60deg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-17887.48295795</v>
+        <v>-135.5726184047618</v>
       </c>
       <c r="C25" t="n">
-        <v>9645.975405100715</v>
+        <v>3703.054068747163</v>
       </c>
       <c r="D25" t="n">
-        <v>162.8205356666666</v>
+        <v>369.3010496190477</v>
       </c>
       <c r="E25" t="n">
-        <v>14647.64036153058</v>
+        <v>3008.818236997048</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>130deg</t>
+          <t>-55deg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-398.0607212955715</v>
+        <v>167.4072403285714</v>
       </c>
       <c r="C26" t="n">
-        <v>1977.187924143474</v>
+        <v>3888.536470008535</v>
       </c>
       <c r="D26" t="n">
-        <v>916.9934332380951</v>
+        <v>129.2094811428573</v>
       </c>
       <c r="E26" t="n">
-        <v>3737.332446576849</v>
+        <v>3735.514906768211</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0deg</t>
+          <t>-50deg</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77.61156191095239</v>
+        <v>-210.3345719809525</v>
       </c>
       <c r="C27" t="n">
-        <v>360.3248032899532</v>
+        <v>4027.229940948213</v>
       </c>
       <c r="D27" t="n">
-        <v>1357.749577789048</v>
+        <v>477.819168904762</v>
       </c>
       <c r="E27" t="n">
-        <v>10136.7001419032</v>
+        <v>4504.294420721045</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>95deg</t>
+          <t>-45deg</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1028.088287400953</v>
+        <v>-400.4930320380952</v>
       </c>
       <c r="C28" t="n">
-        <v>1314.144804067497</v>
+        <v>4279.042449734377</v>
       </c>
       <c r="D28" t="n">
-        <v>286.3168905714286</v>
+        <v>1160.624957771428</v>
       </c>
       <c r="E28" t="n">
-        <v>2043.820329560136</v>
+        <v>5252.44990219149</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-130deg</t>
+          <t>-40deg</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>77.61156191095239</v>
+        <v>-707.3816394095238</v>
       </c>
       <c r="C29" t="n">
-        <v>360.3248032899532</v>
+        <v>4040.608493736558</v>
       </c>
       <c r="D29" t="n">
-        <v>1357.749577789048</v>
+        <v>1436.829598666666</v>
       </c>
       <c r="E29" t="n">
-        <v>10136.7001419032</v>
+        <v>5994.458756151136</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-40deg</t>
+          <t>-35deg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-707.3816394095238</v>
+        <v>-536.9723312142858</v>
       </c>
       <c r="C30" t="n">
-        <v>4040.608493736558</v>
+        <v>3715.551167445239</v>
       </c>
       <c r="D30" t="n">
-        <v>1436.829598666666</v>
+        <v>1233.559151195238</v>
       </c>
       <c r="E30" t="n">
-        <v>5994.458756151136</v>
+        <v>6750.70572390641</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>90deg</t>
+          <t>-30deg</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1299.715836504286</v>
+        <v>-383.1280402857143</v>
       </c>
       <c r="C31" t="n">
-        <v>1713.180558803326</v>
+        <v>3310.670987306264</v>
       </c>
       <c r="D31" t="n">
-        <v>338.2293649047619</v>
+        <v>1228.79880837619</v>
       </c>
       <c r="E31" t="n">
-        <v>2105.694011243545</v>
+        <v>7313.699439512969</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-35deg</t>
+          <t>-25deg</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-536.9723312142858</v>
+        <v>-615.5435602295237</v>
       </c>
       <c r="C32" t="n">
-        <v>3715.551167445239</v>
+        <v>2798.012092609699</v>
       </c>
       <c r="D32" t="n">
-        <v>1233.559151195238</v>
+        <v>1390.018021810476</v>
       </c>
       <c r="E32" t="n">
-        <v>6750.70572390641</v>
+        <v>7744.967730938922</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-10deg</t>
+          <t>-20deg</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-312.6346136069524</v>
+        <v>-557.1148521685715</v>
       </c>
       <c r="C33" t="n">
-        <v>1325.910124127219</v>
+        <v>2320.321104358078</v>
       </c>
       <c r="D33" t="n">
-        <v>1556.789162433333</v>
+        <v>1449.623088628571</v>
       </c>
       <c r="E33" t="n">
-        <v>8644.312127488</v>
+        <v>8215.50712509364</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10deg</t>
+          <t>-15deg</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>536.8018833004762</v>
+        <v>-436.1635462228571</v>
       </c>
       <c r="C34" t="n">
-        <v>708.7011279208451</v>
+        <v>1822.424494995602</v>
       </c>
       <c r="D34" t="n">
-        <v>1808.758937947619</v>
+        <v>1505.520628572858</v>
       </c>
       <c r="E34" t="n">
-        <v>9893.604283921479</v>
+        <v>8475.975376894323</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>125deg</t>
+          <t>-10deg</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-262.8317684547619</v>
+        <v>-312.6346136069524</v>
       </c>
       <c r="C35" t="n">
-        <v>1634.086198899528</v>
+        <v>1325.910124127219</v>
       </c>
       <c r="D35" t="n">
-        <v>768.7214315238094</v>
+        <v>1556.789162433333</v>
       </c>
       <c r="E35" t="n">
-        <v>3292.798766235569</v>
+        <v>8644.312127488</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-60deg</t>
+          <t>-5deg</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-135.5726184047618</v>
+        <v>-135.3992166495239</v>
       </c>
       <c r="C36" t="n">
-        <v>3703.054068747163</v>
+        <v>840.7750207239716</v>
       </c>
       <c r="D36" t="n">
-        <v>369.3010496190477</v>
+        <v>1530.761688961904</v>
       </c>
       <c r="E36" t="n">
-        <v>3008.818236997048</v>
+        <v>9132.357629053256</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-85deg</t>
+          <t>0deg</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-110821.4214485644</v>
+        <v>77.61156191095239</v>
       </c>
       <c r="C37" t="n">
-        <v>100463.1227120362</v>
+        <v>360.3248032899532</v>
       </c>
       <c r="D37" t="n">
-        <v>-10137.39880652381</v>
+        <v>1357.749577789048</v>
       </c>
       <c r="E37" t="n">
-        <v>84721.29026376741</v>
+        <v>10136.7001419032</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>35deg</t>
+          <t>5deg</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1654.33462229381</v>
+        <v>316.5345698402857</v>
       </c>
       <c r="C38" t="n">
-        <v>3650.154005619998</v>
+        <v>185.1617305746504</v>
       </c>
       <c r="D38" t="n">
-        <v>1703.691038461905</v>
+        <v>1614.898214014285</v>
       </c>
       <c r="E38" t="n">
-        <v>9574.960850540041</v>
+        <v>9971.056014624251</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>50deg</t>
+          <t>10deg</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2057.729042244333</v>
+        <v>536.8018833004762</v>
       </c>
       <c r="C39" t="n">
-        <v>4563.81199228024</v>
+        <v>708.7011279208451</v>
       </c>
       <c r="D39" t="n">
-        <v>1622.965092209524</v>
+        <v>1808.758937947619</v>
       </c>
       <c r="E39" t="n">
-        <v>6652.383383084692</v>
+        <v>9893.604283921479</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>-140deg</t>
+          <t>15deg</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1210.006117790476</v>
+        <v>787.321396642381</v>
       </c>
       <c r="C40" t="n">
-        <v>3995.641808978025</v>
+        <v>1315.492302624502</v>
       </c>
       <c r="D40" t="n">
-        <v>1370.433535438095</v>
+        <v>1996.752592904762</v>
       </c>
       <c r="E40" t="n">
-        <v>7344.365517704073</v>
+        <v>9950.227710343732</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>120deg</t>
+          <t>20deg</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-84.91824360904762</v>
+        <v>1035.417178004143</v>
       </c>
       <c r="C41" t="n">
-        <v>1215.042502358468</v>
+        <v>1945.699123311328</v>
       </c>
       <c r="D41" t="n">
-        <v>570.5863263809524</v>
+        <v>2070.318666952381</v>
       </c>
       <c r="E41" t="n">
-        <v>2886.08437431902</v>
+        <v>10034.03022671369</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-145deg</t>
+          <t>25deg</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1153.835657014286</v>
+        <v>1260.921941785714</v>
       </c>
       <c r="C42" t="n">
-        <v>3685.894746668404</v>
+        <v>2590.27922831642</v>
       </c>
       <c r="D42" t="n">
-        <v>1592.303583604762</v>
+        <v>2081.770262552381</v>
       </c>
       <c r="E42" t="n">
-        <v>7972.101645429689</v>
+        <v>9935.443056978445</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-170deg</t>
+          <t>30deg</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>224.3542925947619</v>
+        <v>1464.965918666667</v>
       </c>
       <c r="C43" t="n">
-        <v>949.5655674544259</v>
+        <v>3157.554704016287</v>
       </c>
       <c r="D43" t="n">
-        <v>1243.019115852381</v>
+        <v>1968.68173028381</v>
       </c>
       <c r="E43" t="n">
-        <v>10626.70122817451</v>
+        <v>9642.658386653295</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>-30deg</t>
+          <t>35deg</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-383.1280402857143</v>
+        <v>1654.33462229381</v>
       </c>
       <c r="C44" t="n">
-        <v>3310.670987306264</v>
+        <v>3650.154005619998</v>
       </c>
       <c r="D44" t="n">
-        <v>1228.79880837619</v>
+        <v>1703.691038461905</v>
       </c>
       <c r="E44" t="n">
-        <v>7313.699439512969</v>
+        <v>9574.960850540041</v>
       </c>
     </row>
     <row r="45">
@@ -1294,292 +1294,292 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-50deg</t>
+          <t>45deg</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-210.3345719809525</v>
+        <v>1968.132179120476</v>
       </c>
       <c r="C46" t="n">
-        <v>4027.229940948213</v>
+        <v>4409.554495160801</v>
       </c>
       <c r="D46" t="n">
-        <v>477.819168904762</v>
+        <v>1711.072369461905</v>
       </c>
       <c r="E46" t="n">
-        <v>4504.294420721045</v>
+        <v>7598.926211207297</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>-175deg</t>
+          <t>50deg</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24.8656837827619</v>
+        <v>2057.729042244333</v>
       </c>
       <c r="C47" t="n">
-        <v>335.6092083623426</v>
+        <v>4563.81199228024</v>
       </c>
       <c r="D47" t="n">
-        <v>1356.584471957143</v>
+        <v>1622.965092209524</v>
       </c>
       <c r="E47" t="n">
-        <v>10093.99326714208</v>
+        <v>6652.383383084692</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>150deg</t>
+          <t>55deg</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-703.4134411428571</v>
+        <v>2100.640326898572</v>
       </c>
       <c r="C48" t="n">
-        <v>2820.422321163031</v>
+        <v>4589.585568405176</v>
       </c>
       <c r="D48" t="n">
-        <v>1385.274731876191</v>
+        <v>1464.569943661905</v>
       </c>
       <c r="E48" t="n">
-        <v>7258.821207871728</v>
+        <v>5881.208929283049</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>-95deg</t>
+          <t>60deg</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1221.609143542381</v>
+        <v>2093.8828703</v>
       </c>
       <c r="C49" t="n">
-        <v>2325.759912078654</v>
+        <v>4474.832293693121</v>
       </c>
       <c r="D49" t="n">
-        <v>1902.846852047619</v>
+        <v>1265.74441652381</v>
       </c>
       <c r="E49" t="n">
-        <v>6603.491254678953</v>
+        <v>5136.605277149652</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>70deg</t>
+          <t>65deg</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1960.812143496667</v>
+        <v>2044.01883387619</v>
       </c>
       <c r="C50" t="n">
-        <v>3860.454181526039</v>
+        <v>4228.458676222379</v>
       </c>
       <c r="D50" t="n">
-        <v>864.7028573333331</v>
+        <v>1062.77457152381</v>
       </c>
       <c r="E50" t="n">
-        <v>3764.789414219891</v>
+        <v>4420.849153736214</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>80deg</t>
+          <t>70deg</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1675.013704978572</v>
+        <v>1960.812143496667</v>
       </c>
       <c r="C51" t="n">
-        <v>2882.285077695193</v>
+        <v>3860.454181526039</v>
       </c>
       <c r="D51" t="n">
-        <v>532.5456105238094</v>
+        <v>864.7028573333331</v>
       </c>
       <c r="E51" t="n">
-        <v>2660.093500751368</v>
+        <v>3764.789414219891</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>85deg</t>
+          <t>75deg</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1476.661028461905</v>
+        <v>1834.971976845238</v>
       </c>
       <c r="C52" t="n">
-        <v>2280.972197684488</v>
+        <v>3406.497270186739</v>
       </c>
       <c r="D52" t="n">
-        <v>411.2782690476192</v>
+        <v>682.6981599047618</v>
       </c>
       <c r="E52" t="n">
-        <v>2268.63966174357</v>
+        <v>3175.639481838063</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>-70deg</t>
+          <t>80deg</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1834.784777042381</v>
+        <v>1675.013704978572</v>
       </c>
       <c r="C53" t="n">
-        <v>4201.587417343285</v>
+        <v>2882.285077695193</v>
       </c>
       <c r="D53" t="n">
-        <v>772.542310238095</v>
+        <v>532.5456105238094</v>
       </c>
       <c r="E53" t="n">
-        <v>2060.111725459966</v>
+        <v>2660.093500751368</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>110deg</t>
+          <t>85deg</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>296.2167559095237</v>
+        <v>1476.661028461905</v>
       </c>
       <c r="C54" t="n">
-        <v>538.0584257436873</v>
+        <v>2280.972197684488</v>
       </c>
       <c r="D54" t="n">
-        <v>395.5335662857144</v>
+        <v>411.2782690476192</v>
       </c>
       <c r="E54" t="n">
-        <v>2342.680766757667</v>
+        <v>2268.63966174357</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>65deg</t>
+          <t>90deg</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2044.01883387619</v>
+        <v>1299.715836504286</v>
       </c>
       <c r="C55" t="n">
-        <v>4228.458676222379</v>
+        <v>1713.180558803326</v>
       </c>
       <c r="D55" t="n">
-        <v>1062.77457152381</v>
+        <v>338.2293649047619</v>
       </c>
       <c r="E55" t="n">
-        <v>4420.849153736214</v>
+        <v>2105.694011243545</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>145deg</t>
+          <t>95deg</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-698.3077215095238</v>
+        <v>1028.088287400953</v>
       </c>
       <c r="C56" t="n">
-        <v>2901.832535777132</v>
+        <v>1314.144804067497</v>
       </c>
       <c r="D56" t="n">
-        <v>1361.009366304762</v>
+        <v>286.3168905714286</v>
       </c>
       <c r="E56" t="n">
-        <v>6487.797818021237</v>
+        <v>2043.820329560136</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-160deg</t>
+          <t>100deg</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>629.9694770180953</v>
+        <v>791.0753256652381</v>
       </c>
       <c r="C57" t="n">
-        <v>2205.720489459218</v>
+        <v>908.9109659641111</v>
       </c>
       <c r="D57" t="n">
-        <v>1522.351259352381</v>
+        <v>253.500609904762</v>
       </c>
       <c r="E57" t="n">
-        <v>9668.558856017688</v>
+        <v>2051.938571582224</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>170deg</t>
+          <t>105deg</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-516.4523754671429</v>
+        <v>607.5388687066667</v>
       </c>
       <c r="C58" t="n">
-        <v>1227.100718268684</v>
+        <v>555.5002186796906</v>
       </c>
       <c r="D58" t="n">
-        <v>1542.511387733333</v>
+        <v>251.138499</v>
       </c>
       <c r="E58" t="n">
-        <v>8635.311110406819</v>
+        <v>2157.859867789057</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-165deg</t>
+          <t>110deg</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>441.6166530698573</v>
+        <v>296.2167559095237</v>
       </c>
       <c r="C59" t="n">
-        <v>1589.894158691292</v>
+        <v>538.0584257436873</v>
       </c>
       <c r="D59" t="n">
-        <v>1630.975732561904</v>
+        <v>395.5335662857144</v>
       </c>
       <c r="E59" t="n">
-        <v>9829.555533804167</v>
+        <v>2342.680766757667</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>175deg</t>
+          <t>115deg</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-387.8438563833333</v>
+        <v>-84.91824360904762</v>
       </c>
       <c r="C60" t="n">
-        <v>746.0836886974852</v>
+        <v>1215.042502358468</v>
       </c>
       <c r="D60" t="n">
-        <v>1579.466603230952</v>
+        <v>570.5863263809524</v>
       </c>
       <c r="E60" t="n">
-        <v>9114.687425324315</v>
+        <v>2886.08437431902</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>115deg</t>
+          <t>120deg</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1598,229 +1598,229 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>-90deg</t>
+          <t>125deg</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-568.1584215114284</v>
+        <v>-262.8317684547619</v>
       </c>
       <c r="C62" t="n">
-        <v>50852.67328029735</v>
+        <v>1634.086198899528</v>
       </c>
       <c r="D62" t="n">
-        <v>8923.982683171425</v>
+        <v>768.7214315238094</v>
       </c>
       <c r="E62" t="n">
-        <v>141359.256151088</v>
+        <v>3292.798766235569</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>75deg</t>
+          <t>130deg</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1834.971976845238</v>
+        <v>-398.0607212955715</v>
       </c>
       <c r="C63" t="n">
-        <v>3406.497270186739</v>
+        <v>1977.187924143474</v>
       </c>
       <c r="D63" t="n">
-        <v>682.6981599047618</v>
+        <v>916.9934332380951</v>
       </c>
       <c r="E63" t="n">
-        <v>3175.639481838063</v>
+        <v>3737.332446576849</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-45deg</t>
+          <t>135deg</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-400.4930320380952</v>
+        <v>-466.2586414638096</v>
       </c>
       <c r="C64" t="n">
-        <v>4279.042449734377</v>
+        <v>2399.16475114783</v>
       </c>
       <c r="D64" t="n">
-        <v>1160.624957771428</v>
+        <v>985.2897601190475</v>
       </c>
       <c r="E64" t="n">
-        <v>5252.44990219149</v>
+        <v>4517.062101724706</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>-75deg</t>
+          <t>140deg</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-4822.952057147143</v>
+        <v>-661.3052218666666</v>
       </c>
       <c r="C65" t="n">
-        <v>4849.899016941325</v>
+        <v>2754.834047009056</v>
       </c>
       <c r="D65" t="n">
-        <v>599.2291788571426</v>
+        <v>1276.441974428572</v>
       </c>
       <c r="E65" t="n">
-        <v>4890.736974691083</v>
+        <v>5480.429745189912</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>-150deg</t>
+          <t>145deg</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1033.459658532281</v>
+        <v>-698.3077215095238</v>
       </c>
       <c r="C66" t="n">
-        <v>3281.93771655943</v>
+        <v>2901.832535777132</v>
       </c>
       <c r="D66" t="n">
-        <v>1751.622568120952</v>
+        <v>1361.009366304762</v>
       </c>
       <c r="E66" t="n">
-        <v>8423.722641613707</v>
+        <v>6487.797818021237</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>-65deg</t>
+          <t>150deg</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-636.9687476904762</v>
+        <v>-703.4134411428571</v>
       </c>
       <c r="C67" t="n">
-        <v>3704.736970527907</v>
+        <v>2820.422321163031</v>
       </c>
       <c r="D67" t="n">
-        <v>535.8102426190477</v>
+        <v>1385.274731876191</v>
       </c>
       <c r="E67" t="n">
-        <v>2263.404382377319</v>
+        <v>7258.821207871728</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>-115deg</t>
+          <t>155deg</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>769.0109499289049</v>
+        <v>-735.928520609524</v>
       </c>
       <c r="C68" t="n">
-        <v>3324.227614428866</v>
+        <v>2507.322028432608</v>
       </c>
       <c r="D68" t="n">
-        <v>546.8015591904763</v>
+        <v>1620.754803376191</v>
       </c>
       <c r="E68" t="n">
-        <v>3259.992313578076</v>
+        <v>7580.916267674036</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5deg</t>
+          <t>160deg</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>316.5345698402857</v>
+        <v>-703.4080177509524</v>
       </c>
       <c r="C69" t="n">
-        <v>185.1617305746504</v>
+        <v>2190.129894216443</v>
       </c>
       <c r="D69" t="n">
-        <v>1614.898214014285</v>
+        <v>1644.687025219047</v>
       </c>
       <c r="E69" t="n">
-        <v>9971.056014624251</v>
+        <v>8197.082455689164</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>140deg</t>
+          <t>165deg</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-661.3052218666666</v>
+        <v>-585.1545893257141</v>
       </c>
       <c r="C70" t="n">
-        <v>2754.834047009056</v>
+        <v>1724.848083635922</v>
       </c>
       <c r="D70" t="n">
-        <v>1276.441974428572</v>
+        <v>1449.866905352381</v>
       </c>
       <c r="E70" t="n">
-        <v>5480.429745189912</v>
+        <v>8537.893541451966</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>155deg</t>
+          <t>170deg</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-735.928520609524</v>
+        <v>-516.4523754671429</v>
       </c>
       <c r="C71" t="n">
-        <v>2507.322028432608</v>
+        <v>1227.100718268684</v>
       </c>
       <c r="D71" t="n">
-        <v>1620.754803376191</v>
+        <v>1542.511387733333</v>
       </c>
       <c r="E71" t="n">
-        <v>7580.916267674036</v>
+        <v>8635.311110406819</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>180deg</t>
+          <t>175deg</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-209.1553604107619</v>
+        <v>-387.8438563833333</v>
       </c>
       <c r="C72" t="n">
-        <v>235.6887114596883</v>
+        <v>746.0836886974852</v>
       </c>
       <c r="D72" t="n">
-        <v>1447.838043861904</v>
+        <v>1579.466603230952</v>
       </c>
       <c r="E72" t="n">
-        <v>9422.935194654079</v>
+        <v>9114.687425324315</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20deg</t>
+          <t>180deg</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1035.417178004143</v>
+        <v>-209.1553604107619</v>
       </c>
       <c r="C73" t="n">
-        <v>1945.699123311328</v>
+        <v>235.6887114596883</v>
       </c>
       <c r="D73" t="n">
-        <v>2070.318666952381</v>
+        <v>1447.838043861904</v>
       </c>
       <c r="E73" t="n">
-        <v>10034.03022671369</v>
+        <v>9422.935194654079</v>
       </c>
     </row>
   </sheetData>
